--- a/data/sites/hr/Employee Relations/employee-relations-case-tracker.xlsx
+++ b/data/sites/hr/Employee Relations/employee-relations-case-tracker.xlsx
@@ -7,7 +7,18 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Architecture" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Controls" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 KPIs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,11 +38,15 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,13 +75,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -141,6 +157,186 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4572000" cy="1524000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,19 +628,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee Relations Case Tracker</t>
+          <t>Employee Relations Case Tracker - Section 1: Executive Summary &amp; Scope</t>
         </is>
       </c>
     </row>
@@ -455,104 +651,2170 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 1 (Executive Summary &amp; Scope) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Defines the operational charter, scope boundaries, and executive accountability.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 1.1: Average case resolution time target is 10 business days. Secondary control 1.2: Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Case Type</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Days Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Accommodation</t>
+          <t>Conduct</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Accommodation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Harassment Complaint</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Section 1 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 10: Cross-Functional Dependencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 10 (Cross-Functional Dependencies) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Documents upstream and downstream team dependencies and service-level commitments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 10.1: Cases open longer than 20 business days are escalated to the VP of People. Secondary control 10.2: Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 10 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 10 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 11: Continuous Improvement Roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 11 (Continuous Improvement Roadmap) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 11.1: Case types include conduct, performance, accommodation, and harassment complaints. Secondary control 11.2: All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 11 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 11 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Records document lineage, governance metadata, version history, and owner sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 12.1: All case notes are stored in the restricted Employee Relations case file, not this tracker. Secondary control 12.2: Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 12 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 12 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 2: Architecture &amp; Process Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 2 (Architecture &amp; Process Flow) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Maps end-to-end process stages, handoff gates, and system-of-record integrations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 2.1: Cases open longer than 20 business days are escalated to the VP of People. Secondary control 2.2: Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 2 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 2 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 3: Governance Standards &amp; Controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 3 (Governance Standards &amp; Controls) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Establishes mandatory compliance controls, approval thresholds, and audit evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 3.1: Case types include conduct, performance, accommodation, and harassment complaints. Secondary control 3.2: All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 3 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 3 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 4: Operational KPIs &amp; Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 4 (Operational KPIs &amp; Benchmarks) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Tracks baseline performance, target SLAs, and quarterly benchmark progression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 4.1: All case notes are stored in the restricted Employee Relations case file, not this tracker. Secondary control 4.2: Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 4 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 4 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 5: Roles, Responsibilities &amp; RACI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 5 (Roles, Responsibilities &amp; RACI) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Clarifies ownership across accountable executives, operational leads, and reviewers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 5.1: Average case resolution time target is 10 business days. Secondary control 5.2: Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 5 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 5 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 6: Standard Operating Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 6 (Standard Operating Procedures) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Provides step-by-step execution checklists, intake criteria, and verification gates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 6.1: Cases open longer than 20 business days are escalated to the VP of People. Secondary control 6.2: Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 6 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 6 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 7: Risk Register &amp; Mitigations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 7 (Risk Register &amp; Mitigations) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Catalogs operational, compliance, and delivery risks alongside preventive mitigations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 7.1: Case types include conduct, performance, accommodation, and harassment complaints. Secondary control 7.2: All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 7 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 7 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 8: Quality Assurance &amp; Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 8 (Quality Assurance &amp; Audits) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 8.1: All case notes are stored in the restricted Employee Relations case file, not this tracker. Secondary control 8.2: Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 8 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 8 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employee Relations Case Tracker - Section 9: Exception Handling &amp; Escalations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 9 (Exception Handling &amp; Escalations) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Operational requirement 9.1: Average case resolution time target is 10 business days. Secondary control 9.2: Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Case Type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Days Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Conduct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Accommodation</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Harassment Complaint</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sec-9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Stage 9 Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Governance Checkpoints</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Average case resolution time target is 10 business days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>• Section 9 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/sites/hr/Employee Relations/employee-relations-case-tracker.xlsx
+++ b/data/sites/hr/Employee Relations/employee-relations-case-tracker.xlsx
@@ -14,11 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 RACI Matrix" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Procedures" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Risk Register" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Quality Audit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09 Escalations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 SLAs" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Roadmap" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Sign-off" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08 Sign-off" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -250,66 +246,6 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4572000" cy="1524000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -789,559 +725,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Employee Relations Case Tracker - Section 10: Cross-Functional Dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 10 (Cross-Functional Dependencies) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Documents upstream and downstream team dependencies and service-level commitments.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 10.1: Cases open longer than 20 business days are escalated to the VP of People. Secondary control 10.2: Case types include conduct, performance, accommodation, and harassment complaints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Case Type</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Days Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Accommodation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Harassment Complaint</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 10 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 10 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Employee Relations Case Tracker - Section 11: Continuous Improvement Roadmap</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 11 (Continuous Improvement Roadmap) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Schedules quarterly optimization milestones, automation targets, and capability reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 11.1: Case types include conduct, performance, accommodation, and harassment complaints. Secondary control 11.2: All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Case Type</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Days Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Accommodation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Harassment Complaint</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-11</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 11 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Case types include conduct, performance, accommodation, and harassment complaints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 11 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Employee Relations Case Tracker - Section 12: Appendix, Lineage &amp; Sign-off</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 12 (Appendix, Lineage &amp; Sign-off) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Records document lineage, governance metadata, version history, and owner sign-off.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 12.1: All case notes are stored in the restricted Employee Relations case file, not this tracker. Secondary control 12.2: Average case resolution time target is 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Case Type</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Days Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Accommodation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Harassment Complaint</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-12</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 12 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• All case notes are stored in the restricted Employee Relations case file, not this tracker.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Average case resolution time target is 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 12 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2467,7 +1850,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Employee Relations Case Tracker - Section 8: Quality Assurance &amp; Audits</t>
+          <t>Employee Relations Case Tracker - Section 8: Appendix, Lineage &amp; Sign-off</t>
         </is>
       </c>
     </row>
@@ -2481,7 +1864,7 @@
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 8 (Quality Assurance &amp; Audits) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Specifies sampling frequencies, inspection tolerances, and nonconformance workflows.</t>
+          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 8 (Appendix, Lineage &amp; Sign-off) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Records document lineage, governance metadata, version history, and owner sign-off.</t>
         </is>
       </c>
     </row>
@@ -2619,191 +2002,6 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>• Section 8 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Employee Relations Case Tracker - Section 9: Exception Handling &amp; Escalations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>HR Knowledge Hub | Employee Relations | Owner: Ben Okafor  |  Last updated: October 30, 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Log of open and closed employee relations cases with case type, status, and days open, used to monitor caseload and resolution time. Section 9 (Exception Handling &amp; Escalations) applies to Employee Relations within HR Knowledge Hub and is maintained by Ben Okafor. Outlines severity tiers, response SLAs, and cross-functional escalation paths.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Operational requirement 9.1: Average case resolution time target is 10 business days. Secondary control 9.2: Cases open longer than 20 business days are escalated to the VP of People.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Case Type</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Days Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Conduct</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Accommodation</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Harassment Complaint</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sec-9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stage 9 Verified</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Governance Checkpoints</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>• Average case resolution time target is 10 business days.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>• Cases open longer than 20 business days are escalated to the VP of People.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>• Section 9 review cadence is tracked by Ben Okafor under Employee Relations governance.</t>
         </is>
       </c>
     </row>
